--- a/design/tables/ShopUpgrade.xlsx
+++ b/design/tables/ShopUpgrade.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopUpgrade" sheetId="1" r:id="Rfd0a993214204a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopUpgrade" sheetId="1" r:id="Rbe783f2328dd4b38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,6 +297,15 @@
       <x:c r="H1" s="1" t="str">
         <x:v>descriptionKey</x:v>
       </x:c>
+      <x:c r="I1" t="str">
+        <x:v>minShelves</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>minSold</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>设备图标</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="str">
@@ -323,6 +332,15 @@
       <x:c r="H2" s="1" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="I2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="1" t="str">
@@ -349,16 +367,50 @@
       <x:c r="H3" s="1" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="I3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K3" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str"/>
-      <x:c r="B4" s="1" t="str"/>
-      <x:c r="C4" s="1" t="str"/>
-      <x:c r="D4" s="1" t="str"/>
-      <x:c r="E4" s="1" t="str"/>
-      <x:c r="F4" s="1" t="str"/>
-      <x:c r="G4" s="1" t="str"/>
-      <x:c r="H4" s="1" t="str"/>
+      <x:c r="A4" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>tier</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>cost</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>value</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="str">
+        <x:v>nameKey</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="str">
+        <x:v>descriptionKey</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>minShelves</x:v>
+      </x:c>
+      <x:c r="J4" t="str">
+        <x:v>minSold</x:v>
+      </x:c>
+      <x:c r="K4" t="str">
+        <x:v>VisualSkin图片引用</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -385,6 +437,15 @@
       <x:c r="H5" s="3" t="str">
         <x:v>descriptionKey</x:v>
       </x:c>
+      <x:c r="I5" t="str">
+        <x:v>minShelves</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>minSold</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>imageKey</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="1" t="n">
@@ -411,6 +472,15 @@
       <x:c r="H6" s="1" t="str">
         <x:v>shop.upgrade.checkout.1</x:v>
       </x:c>
+      <x:c r="I6" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>shop_checkout</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="1" t="n">
@@ -436,6 +506,15 @@
       </x:c>
       <x:c r="H7" s="1" t="str">
         <x:v>shop.upgrade.checkout.2</x:v>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>shop_checkout</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
@@ -463,31 +542,49 @@
       <x:c r="H8" s="1" t="str">
         <x:v>shop.upgrade.checkout.3</x:v>
       </x:c>
+      <x:c r="I8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>shop_checkout</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="1" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="1" t="str">
-        <x:v>restock_1</x:v>
+        <x:v>checkout_4</x:v>
       </x:c>
       <x:c r="C9" s="1" t="str">
-        <x:v>restock</x:v>
+        <x:v>checkout</x:v>
       </x:c>
       <x:c r="D9" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E9" s="1" t="n">
-        <x:v>60</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="F9" s="1" t="n">
-        <x:v>0.3</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="G9" s="1" t="str">
-        <x:v>shop.upgrade.restock</x:v>
+        <x:v>shop.upgrade.checkout</x:v>
       </x:c>
       <x:c r="H9" s="1" t="str">
-        <x:v>shop.upgrade.restock.1</x:v>
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>shop_checkout</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -495,25 +592,34 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="str">
-        <x:v>restock_2</x:v>
+        <x:v>checkout_5</x:v>
       </x:c>
       <x:c r="C10" s="1" t="str">
-        <x:v>restock</x:v>
+        <x:v>checkout</x:v>
       </x:c>
       <x:c r="D10" s="1" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="1" t="n">
-        <x:v>180</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="F10" s="1" t="n">
-        <x:v>0.65</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>shop.upgrade.restock</x:v>
+        <x:v>shop.upgrade.checkout</x:v>
       </x:c>
       <x:c r="H10" s="1" t="str">
-        <x:v>shop.upgrade.restock.2</x:v>
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" t="str">
+        <x:v>shop_checkout</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -521,25 +627,34 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="1" t="str">
-        <x:v>restock_3</x:v>
+        <x:v>checkout_6</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
-        <x:v>restock</x:v>
+        <x:v>checkout</x:v>
       </x:c>
       <x:c r="D11" s="1" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E11" s="1" t="n">
-        <x:v>420</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="F11" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G11" s="1" t="str">
-        <x:v>shop.upgrade.restock</x:v>
+        <x:v>shop.upgrade.checkout</x:v>
       </x:c>
       <x:c r="H11" s="1" t="str">
-        <x:v>shop.upgrade.restock.3</x:v>
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>shop_checkout</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -547,25 +662,34 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="1" t="str">
-        <x:v>shelves_1</x:v>
+        <x:v>checkout_7</x:v>
       </x:c>
       <x:c r="C12" s="1" t="str">
-        <x:v>shelves</x:v>
+        <x:v>checkout</x:v>
       </x:c>
       <x:c r="D12" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E12" s="1" t="n">
-        <x:v>120</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="F12" s="1" t="n">
-        <x:v>3</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="G12" s="1" t="str">
-        <x:v>shop.upgrade.shelves</x:v>
+        <x:v>shop.upgrade.checkout</x:v>
       </x:c>
       <x:c r="H12" s="1" t="str">
-        <x:v>shop.upgrade.shelves.1</x:v>
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>shop_checkout</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -573,25 +697,1294 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="1" t="str">
+        <x:v>checkout_8</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="str">
+        <x:v>checkout</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="str">
+        <x:v>shop.upgrade.checkout</x:v>
+      </x:c>
+      <x:c r="H13" s="1" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>shop_checkout</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>checkout_9</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>checkout</x:v>
+      </x:c>
+      <x:c r="D14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E14" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="F14" t="n">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>shop.upgrade.checkout</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" t="str">
+        <x:v>shop_checkout</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>checkout_10</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>checkout</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="F15" t="n">
+        <x:v>4.2</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>shop.upgrade.checkout</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" t="str">
+        <x:v>shop_checkout</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>restock_1</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>shop.upgrade.restock.1</x:v>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>restock_2</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>shop.upgrade.restock.2</x:v>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>restock_3</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>shop.upgrade.restock.3</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>restock_4</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>restock_5</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>restock_6</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E21" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="F21" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>restock_7</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>restock_8</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G23" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>restock_9</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G24" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>restock_10</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>restock</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>shop.upgrade.restock</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>shop_crate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>capacity_1</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>shop.upgrade.capacity</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>capacity_2</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>shop.upgrade.capacity</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>capacity_3</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>shop.upgrade.capacity</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>capacity_4</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>shop.upgrade.capacity</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>capacity_5</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>capacity</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>24000</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>shop.upgrade.capacity</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>attraction_1</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="G31" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H31" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>attraction_2</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="G32" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H32" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>attraction_3</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E33" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="F33" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K33" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>attraction_4</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K34" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>attraction_5</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>0.85</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K35" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>attraction_6</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="G36" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H36" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>attraction_7</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K37" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>attraction_8</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>8500</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>attraction_9</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>13000</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>attraction_10</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>attraction</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>shop.upgrade.attraction</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>icon_store</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>service_1</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>service</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>shop.upgrade.service</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>shop_bag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>service_2</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>service</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>shop.upgrade.service</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>shop_bag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>service_3</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>service</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>shop.upgrade.service</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>shop_bag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>service_4</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>service</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>shop.upgrade.service</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>shop_bag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>service_5</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>service</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>24000</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>shop.upgrade.service</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>shop_bag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>shelves_1</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>shelves</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>shop.upgrade.shelves</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>shop.upgrade.shelves.1</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
         <x:v>shelves_2</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="str">
+      <x:c r="C47" t="str">
         <x:v>shelves</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="n">
+      <x:c r="D47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="n">
+      <x:c r="F47" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="str">
+      <x:c r="G47" t="str">
         <x:v>shop.upgrade.shelves</x:v>
       </x:c>
-      <x:c r="H13" s="1" t="str">
+      <x:c r="H47" t="str">
         <x:v>shop.upgrade.shelves.2</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>shelves_3</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>shelves</x:v>
+      </x:c>
+      <x:c r="D48" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>6000</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>shop.upgrade.shelves</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J48" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>shop_shelf</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>shelves_4</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>shelves</x:v>
+      </x:c>
+      <x:c r="D49" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E49" t="n">
+        <x:v>24000</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>shop.upgrade.shelves</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>shop.compare</x:v>
+      </x:c>
+      <x:c r="I49" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J49" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>shop_shelf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
